--- a/berekeningen/geleiders.xlsx
+++ b/berekeningen/geleiders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\svenk\Documents\GitHub\ProjectGearDeburr\berekeningen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3870EB1D-229B-49DC-9BDB-4F211876E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67278B0-A3B0-4958-B631-F55EBD6F9CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="23385" xr2:uid="{CBB8AF3F-DA56-4131-A4B9-DAA22F42650C}"/>
+    <workbookView xWindow="2940" yWindow="4245" windowWidth="34890" windowHeight="15345" xr2:uid="{CBB8AF3F-DA56-4131-A4B9-DAA22F42650C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>inputs</t>
   </si>
@@ -175,12 +175,30 @@
   <si>
     <t>trekkracht</t>
   </si>
+  <si>
+    <t>C0</t>
+  </si>
+  <si>
+    <t>trekkracht geleider</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>drukkracht geleider</t>
+  </si>
+  <si>
+    <t>punt 2 sterk genoeg</t>
+  </si>
+  <si>
+    <t>punt 3 sterk genoeg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +210,14 @@
       <vertAlign val="subscript"/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -226,18 +252,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -634,27 +663,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F929C61E-BD1C-425B-8904-DE560C5912B2}">
-  <dimension ref="B2:I26"/>
+  <dimension ref="B2:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -664,20 +695,23 @@
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -687,21 +721,22 @@
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="2"/>
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <f>C9*C5/C7</f>
         <v>39.24</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
       <c r="C5" s="2">
         <f>C4/1000</f>
@@ -710,21 +745,22 @@
       <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="2"/>
+      <c r="G5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="2">
-        <f>C9+G4</f>
+      <c r="H5" s="2">
+        <f>C9+H4</f>
         <v>68.67</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
@@ -734,8 +770,18 @@
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>IF(C11&gt;H4, "ja", "nee")</f>
+        <v>ja</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <f>C6/1000</f>
@@ -744,8 +790,18 @@
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="E7" s="4"/>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <f>IF(C10&gt;H5, "ja", "nee")</f>
+        <v>ja</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
@@ -755,8 +811,9 @@
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="2">
         <f>C8*9.81</f>
@@ -765,8 +822,37 @@
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8330</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="2">
+        <v>13500</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -778,7 +864,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -788,7 +874,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -798,7 +884,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -808,7 +894,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>

--- a/berekeningen/geleiders.xlsx
+++ b/berekeningen/geleiders.xlsx
@@ -1010,4 +1010,207 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73a9dcd17d910bedbbfcf71dea21917b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a2fda66a0a1023ae4e3cd4e4288c789" ns2:_="">
+    <xsd:import namespace="71fe66e1-c1d4-4b45-94dc-995258161867"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="71fe66e1-c1d4-4b45-94dc-995258161867" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ea23b583-fc58-4aef-a739-6987dbfb3358" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28B78CA7-57C1-4B71-B76B-14946278A1A1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03867666-86B6-4E5D-8681-EFC20EBE91E2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7E2228-A1ED-4B44-B6AB-9EE73E2FA829}"/>
 </file>
--- a/berekeningen/geleiders.xlsx
+++ b/berekeningen/geleiders.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\svenk\Documents\GitHub\ProjectGearDeburr\berekeningen\"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -63,6 +63,9 @@
     <t>inputs</t>
   </si>
   <si>
+    <t>berekeningen</t>
+  </si>
+  <si>
     <t>grootheid</t>
   </si>
   <si>
@@ -70,6 +73,94 @@
   </si>
   <si>
     <t>eenheid</t>
+  </si>
+  <si>
+    <t>opmerking</t>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>drukkracht</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>trekkracht</t>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>punt 2 sterk genoeg</t>
+  </si>
+  <si>
+    <t>punt 3 sterk genoeg</t>
   </si>
   <si>
     <r>
@@ -88,94 +179,9 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>berekeningen</t>
-  </si>
-  <si>
-    <t>mm</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>kg</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <r>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>opmerking</t>
-  </si>
-  <si>
-    <t>drukkracht</t>
-  </si>
-  <si>
-    <t>trekkracht</t>
-  </si>
-  <si>
     <t>C0</t>
   </si>
   <si>
@@ -186,19 +192,13 @@
   </si>
   <si>
     <t>drukkracht geleider</t>
-  </si>
-  <si>
-    <t>punt 2 sterk genoeg</t>
-  </si>
-  <si>
-    <t>punt 3 sterk genoeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,14 +260,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -664,7 +664,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F929C61E-BD1C-425B-8904-DE560C5912B2}">
   <dimension ref="B2:J26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -677,102 +677,102 @@
     <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="18">
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2">
         <v>200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H4" s="2">
         <f>C9*C5/C7</f>
         <v>39.24</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="18">
       <c r="B5" s="2"/>
       <c r="C5" s="2">
         <f>C4/1000</f>
         <v>0.2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2">
         <f>C9+H4</f>
         <v>68.67</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="18">
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>150</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="str">
         <f>IF(C11&gt;H4, "ja", "nee")</f>
@@ -781,18 +781,18 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10">
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <f>C6/1000</f>
         <v>0.15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="G7" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="str">
         <f>IF(C10&gt;H5, "ja", "nee")</f>
@@ -801,208 +801,208 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="2:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="18">
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10">
       <c r="B9" s="2"/>
       <c r="C9" s="2">
         <f>C8*9.81</f>
         <v>29.43</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10">
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2">
         <v>8330</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
         <v>13500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="e" vm="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="4" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1013,8 +1013,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73a9dcd17d910bedbbfcf71dea21917b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a2fda66a0a1023ae4e3cd4e4288c789" ns2:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="76f0660c00307a9fc6b8f016be658328">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47a6827155b2c9d8b55185a8ae1cad52" ns2:_="">
     <xsd:import namespace="71fe66e1-c1d4-4b45-94dc-995258161867"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -1184,27 +1203,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28B78CA7-57C1-4B71-B76B-14946278A1A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7E2228-A1ED-4B44-B6AB-9EE73E2FA829}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1212,5 +1212,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7E2228-A1ED-4B44-B6AB-9EE73E2FA829}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A0ECC37-BFD3-4DE5-B892-85BDD9FD5C10}"/>
 </file>